--- a/plantillas/7_Control_Directivo/01_Control_Operativo_Semanal.xlsx
+++ b/plantillas/7_Control_Directivo/01_Control_Operativo_Semanal.xlsx
@@ -1520,7 +1520,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -2177,7 +2177,7 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
